--- a/results/04_final_refined_daily_hydroclimate_data/601/Daily_all_temperatures.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/601/Daily_all_temperatures.xlsx
@@ -489,10 +489,10 @@
         <v>25</v>
       </c>
       <c r="E2" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="F2" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -526,7 +526,7 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>24.1</v>
+        <v>24.41</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
@@ -547,12 +547,8 @@
       <c r="D5" t="n">
         <v>23.9</v>
       </c>
-      <c r="E5" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>16.5</v>
-      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -570,12 +566,8 @@
       <c r="D6" t="n">
         <v>21.5</v>
       </c>
-      <c r="E6" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F6" t="n">
-        <v>17.7</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -613,15 +605,9 @@
       <c r="C8" t="n">
         <v>7</v>
       </c>
-      <c r="D8" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="E8" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="F8" t="n">
-        <v>17.9</v>
-      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -659,15 +645,9 @@
       <c r="C10" t="n">
         <v>9</v>
       </c>
-      <c r="D10" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="E10" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="F10" t="n">
-        <v>17.6</v>
-      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -699,15 +679,9 @@
       <c r="C12" t="n">
         <v>11</v>
       </c>
-      <c r="D12" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="E12" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="F12" t="n">
-        <v>18.7</v>
-      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -745,15 +719,9 @@
       <c r="C14" t="n">
         <v>13</v>
       </c>
-      <c r="D14" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="E14" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="F14" t="n">
-        <v>17.5</v>
-      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -772,10 +740,10 @@
         <v>21.9</v>
       </c>
       <c r="E15" t="n">
-        <v>15.7</v>
+        <v>14.7</v>
       </c>
       <c r="F15" t="n">
-        <v>18.8</v>
+        <v>18.3</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
@@ -814,7 +782,9 @@
       <c r="C17" t="n">
         <v>16</v>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="n">
+        <v>22.6</v>
+      </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
@@ -831,15 +801,9 @@
       <c r="C18" t="n">
         <v>17</v>
       </c>
-      <c r="D18" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="E18" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="F18" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -858,7 +822,7 @@
         <v>23.4</v>
       </c>
       <c r="E19" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="F19" t="n">
         <v>18.9</v>
@@ -934,15 +898,9 @@
       <c r="C23" t="n">
         <v>22</v>
       </c>
-      <c r="D23" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="E23" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="F23" t="n">
-        <v>18.8</v>
-      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -997,9 +955,15 @@
       <c r="C26" t="n">
         <v>25</v>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+      <c r="D26" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F26" t="n">
+        <v>19.1</v>
+      </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -1014,15 +978,9 @@
       <c r="C27" t="n">
         <v>26</v>
       </c>
-      <c r="D27" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="E27" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="F27" t="n">
-        <v>18.7</v>
-      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -1038,10 +996,10 @@
         <v>27</v>
       </c>
       <c r="D28" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="E28" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="F28" t="n">
         <v>19.1</v>
@@ -1083,15 +1041,9 @@
       <c r="C30" t="n">
         <v>29</v>
       </c>
-      <c r="D30" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="E30" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="F30" t="n">
-        <v>18.5</v>
-      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -1106,15 +1058,9 @@
       <c r="C31" t="n">
         <v>30</v>
       </c>
-      <c r="D31" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="E31" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="F31" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -1130,13 +1076,13 @@
         <v>31</v>
       </c>
       <c r="D32" t="n">
-        <v>23.4</v>
+        <v>34.8</v>
       </c>
       <c r="E32" t="n">
-        <v>12.6</v>
+        <v>30.2</v>
       </c>
       <c r="F32" t="n">
-        <v>18</v>
+        <v>32.5</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>

--- a/results/04_final_refined_daily_hydroclimate_data/601/Daily_all_temperatures.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/601/Daily_all_temperatures.xlsx
@@ -486,13 +486,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="E2" t="n">
         <v>13.6</v>
       </c>
       <c r="F2" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -525,9 +525,7 @@
       <c r="C4" t="n">
         <v>3</v>
       </c>
-      <c r="D4" t="n">
-        <v>24.41</v>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
@@ -544,9 +542,7 @@
       <c r="C5" t="n">
         <v>4</v>
       </c>
-      <c r="D5" t="n">
-        <v>23.9</v>
-      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
@@ -563,9 +559,7 @@
       <c r="C6" t="n">
         <v>5</v>
       </c>
-      <c r="D6" t="n">
-        <v>21.5</v>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
@@ -583,13 +577,13 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>22.5</v>
+        <v>23.7</v>
       </c>
       <c r="E7" t="n">
-        <v>13.7</v>
+        <v>13.5</v>
       </c>
       <c r="F7" t="n">
-        <v>18.1</v>
+        <v>18.6</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -622,15 +616,9 @@
       <c r="C9" t="n">
         <v>8</v>
       </c>
-      <c r="D9" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="E9" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="F9" t="n">
-        <v>18.7</v>
-      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -696,15 +684,9 @@
       <c r="C13" t="n">
         <v>12</v>
       </c>
-      <c r="D13" t="n">
-        <v>25</v>
-      </c>
-      <c r="E13" t="n">
-        <v>14</v>
-      </c>
-      <c r="F13" t="n">
-        <v>19.5</v>
-      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -736,15 +718,9 @@
       <c r="C15" t="n">
         <v>14</v>
       </c>
-      <c r="D15" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="E15" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="F15" t="n">
-        <v>18.3</v>
-      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -759,15 +735,9 @@
       <c r="C16" t="n">
         <v>15</v>
       </c>
-      <c r="D16" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="E16" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="F16" t="n">
-        <v>17.5</v>
-      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
@@ -785,8 +755,12 @@
       <c r="D17" t="n">
         <v>22.6</v>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F17" t="n">
+        <v>18.2</v>
+      </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -818,15 +792,9 @@
       <c r="C19" t="n">
         <v>18</v>
       </c>
-      <c r="D19" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="E19" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="F19" t="n">
-        <v>18.9</v>
-      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -858,15 +826,9 @@
       <c r="C21" t="n">
         <v>20</v>
       </c>
-      <c r="D21" t="n">
-        <v>22</v>
-      </c>
-      <c r="E21" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="F21" t="n">
-        <v>17.9</v>
-      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -881,9 +843,15 @@
       <c r="C22" t="n">
         <v>21</v>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
+      <c r="D22" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="F22" t="n">
+        <v>18.1</v>
+      </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -915,15 +883,9 @@
       <c r="C24" t="n">
         <v>23</v>
       </c>
-      <c r="D24" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="E24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="F24" t="n">
-        <v>17.8</v>
-      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
@@ -955,15 +917,9 @@
       <c r="C26" t="n">
         <v>25</v>
       </c>
-      <c r="D26" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="E26" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F26" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -978,9 +934,15 @@
       <c r="C27" t="n">
         <v>26</v>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
+      <c r="D27" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E27" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F27" t="n">
+        <v>18.2</v>
+      </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -995,15 +957,9 @@
       <c r="C28" t="n">
         <v>27</v>
       </c>
-      <c r="D28" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="E28" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="F28" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -1018,15 +974,9 @@
       <c r="C29" t="n">
         <v>28</v>
       </c>
-      <c r="D29" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="E29" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="F29" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -1075,15 +1025,9 @@
       <c r="C32" t="n">
         <v>31</v>
       </c>
-      <c r="D32" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="E32" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="F32" t="n">
-        <v>32.5</v>
-      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>

--- a/results/04_final_refined_daily_hydroclimate_data/601/Daily_all_temperatures.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/601/Daily_all_temperatures.xlsx
@@ -492,7 +492,7 @@
         <v>13.6</v>
       </c>
       <c r="F2" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -508,9 +508,15 @@
       <c r="C3" t="n">
         <v>2</v>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>24</v>
+      </c>
+      <c r="E3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>19.1</v>
+      </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -525,9 +531,15 @@
       <c r="C4" t="n">
         <v>3</v>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="F4" t="n">
+        <v>18</v>
+      </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -542,9 +554,15 @@
       <c r="C5" t="n">
         <v>4</v>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>18.98</v>
+      </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -559,9 +577,15 @@
       <c r="C6" t="n">
         <v>5</v>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F6" t="n">
+        <v>17.7</v>
+      </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -577,13 +601,13 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>23.7</v>
+        <v>22.5</v>
       </c>
       <c r="E7" t="n">
-        <v>13.5</v>
+        <v>13.7</v>
       </c>
       <c r="F7" t="n">
-        <v>18.6</v>
+        <v>18.1</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -599,9 +623,15 @@
       <c r="C8" t="n">
         <v>7</v>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="F8" t="n">
+        <v>17.9</v>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -616,9 +646,15 @@
       <c r="C9" t="n">
         <v>8</v>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E9" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>18.7</v>
+      </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -634,7 +670,9 @@
         <v>9</v>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>13.4</v>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -651,7 +689,9 @@
         <v>10</v>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>13.2</v>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -701,9 +741,15 @@
       <c r="C14" t="n">
         <v>13</v>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F14" t="n">
+        <v>17.8</v>
+      </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -753,13 +799,13 @@
         <v>16</v>
       </c>
       <c r="D17" t="n">
-        <v>22.6</v>
+        <v>24</v>
       </c>
       <c r="E17" t="n">
-        <v>13.9</v>
+        <v>11.3</v>
       </c>
       <c r="F17" t="n">
-        <v>18.2</v>
+        <v>17</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
@@ -775,9 +821,15 @@
       <c r="C18" t="n">
         <v>17</v>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+      <c r="D18" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E18" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>18.9</v>
+      </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -792,9 +844,15 @@
       <c r="C19" t="n">
         <v>18</v>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="E19" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="F19" t="n">
+        <v>18.8</v>
+      </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -809,9 +867,15 @@
       <c r="C20" t="n">
         <v>19</v>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="D20" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E20" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F20" t="n">
+        <v>17.9</v>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -826,9 +890,15 @@
       <c r="C21" t="n">
         <v>20</v>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+      <c r="D21" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="E21" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>17.9</v>
+      </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -844,14 +914,10 @@
         <v>21</v>
       </c>
       <c r="D22" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="E22" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="F22" t="n">
-        <v>18.1</v>
-      </c>
+        <v>22.4</v>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -917,9 +983,15 @@
       <c r="C26" t="n">
         <v>25</v>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+      <c r="D26" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F26" t="n">
+        <v>19.1</v>
+      </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -934,15 +1006,9 @@
       <c r="C27" t="n">
         <v>26</v>
       </c>
-      <c r="D27" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="E27" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="F27" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -974,9 +1040,15 @@
       <c r="C29" t="n">
         <v>28</v>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
+      <c r="D29" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="E29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F29" t="n">
+        <v>13.1</v>
+      </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -1025,9 +1097,15 @@
       <c r="C32" t="n">
         <v>31</v>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+      <c r="D32" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E32" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F32" t="n">
+        <v>18</v>
+      </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>

--- a/results/04_final_refined_daily_hydroclimate_data/601/Daily_all_temperatures.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/601/Daily_all_temperatures.xlsx
@@ -486,7 +486,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="E2" t="n">
         <v>13.6</v>
@@ -532,13 +532,13 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>23.2</v>
+        <v>24.1</v>
       </c>
       <c r="E4" t="n">
         <v>12.8</v>
       </c>
       <c r="F4" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -555,14 +555,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="E5" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="F5" t="n">
-        <v>18.98</v>
-      </c>
+        <v>23.8</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -581,10 +577,10 @@
         <v>21.6</v>
       </c>
       <c r="E6" t="n">
-        <v>13.8</v>
+        <v>13.5</v>
       </c>
       <c r="F6" t="n">
-        <v>17.7</v>
+        <v>17.9</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -647,7 +643,7 @@
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="E9" t="n">
         <v>13.8</v>
@@ -670,9 +666,7 @@
         <v>9</v>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="n">
-        <v>13.4</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -689,9 +683,7 @@
         <v>10</v>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="n">
-        <v>13.2</v>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -707,9 +699,15 @@
       <c r="C12" t="n">
         <v>11</v>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="E12" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="F12" t="n">
+        <v>18.9</v>
+      </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -742,13 +740,13 @@
         <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>24.9</v>
+        <v>21.9</v>
       </c>
       <c r="E14" t="n">
-        <v>10.7</v>
+        <v>13.8</v>
       </c>
       <c r="F14" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
@@ -764,9 +762,15 @@
       <c r="C15" t="n">
         <v>14</v>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E15" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="F15" t="n">
+        <v>18.3</v>
+      </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -781,9 +785,15 @@
       <c r="C16" t="n">
         <v>15</v>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="E16" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="F16" t="n">
+        <v>17.5</v>
+      </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
@@ -798,15 +808,9 @@
       <c r="C17" t="n">
         <v>16</v>
       </c>
-      <c r="D17" t="n">
-        <v>24</v>
-      </c>
-      <c r="E17" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="F17" t="n">
-        <v>17</v>
-      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -844,15 +848,9 @@
       <c r="C19" t="n">
         <v>18</v>
       </c>
-      <c r="D19" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="E19" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="F19" t="n">
-        <v>18.8</v>
-      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -868,7 +866,7 @@
         <v>19</v>
       </c>
       <c r="D20" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="E20" t="n">
         <v>13.8</v>
@@ -891,10 +889,10 @@
         <v>20</v>
       </c>
       <c r="D21" t="n">
-        <v>21.4</v>
+        <v>21.9</v>
       </c>
       <c r="E21" t="n">
-        <v>13.3</v>
+        <v>13.8</v>
       </c>
       <c r="F21" t="n">
         <v>17.9</v>
@@ -913,9 +911,7 @@
       <c r="C22" t="n">
         <v>21</v>
       </c>
-      <c r="D22" t="n">
-        <v>22.4</v>
-      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
@@ -1063,9 +1059,15 @@
       <c r="C30" t="n">
         <v>29</v>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+      <c r="D30" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="E30" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="F30" t="n">
+        <v>18.5</v>
+      </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
